--- a/preparing_data/precip_uy/COORDENADAS.xlsx
+++ b/preparing_data/precip_uy/COORDENADAS.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hernanquerbes/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DB0CF6-ECCF-F140-86B0-49E8DC2E4148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja3" sheetId="1" r:id="rId4"/>
+    <sheet name="Hoja3" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Hoja3!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja3!$A$1:$F$149</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1P/J1BmqRjGFNLLqw9ZvCV/U3pqSZ+jB65X7y6lqiSE="/>
@@ -18,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="166">
   <si>
     <t>lat</t>
   </si>
@@ -143,9 +153,6 @@
     <t>Catalan Grande</t>
   </si>
   <si>
-    <t>Cañada Grande</t>
-  </si>
-  <si>
     <t>Rio Negro</t>
   </si>
   <si>
@@ -227,9 +234,6 @@
     <t>Cuaro</t>
   </si>
   <si>
-    <t>Cuchilla Caragauta N</t>
-  </si>
-  <si>
     <t>Cuchilla Caragauta S</t>
   </si>
   <si>
@@ -281,9 +285,6 @@
     <t>Fray Bentos</t>
   </si>
   <si>
-    <t>Goñi</t>
-  </si>
-  <si>
     <t>General Martinez</t>
   </si>
   <si>
@@ -374,9 +375,6 @@
     <t>Paso Campamento</t>
   </si>
   <si>
-    <t>Paso de la Cruz_RN</t>
-  </si>
-  <si>
     <t>Paso Farias</t>
   </si>
   <si>
@@ -455,12 +453,6 @@
     <t>Sarandi de Arapey</t>
   </si>
   <si>
-    <t>Sarandi del Yi</t>
-  </si>
-  <si>
-    <t>Sarandi Grande</t>
-  </si>
-  <si>
     <t>Sequeira</t>
   </si>
   <si>
@@ -522,33 +514,49 @@
   </si>
   <si>
     <t>Zapican</t>
+  </si>
+  <si>
+    <t>Canada Grande</t>
+  </si>
+  <si>
+    <t>Goni</t>
+  </si>
+  <si>
+    <t>Cuchilla Caraguata Norte</t>
+  </si>
+  <si>
+    <t>Paso de la Cruz_rn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -556,7 +564,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -566,42 +574,52 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -791,24 +809,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F998"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="6.71"/>
-    <col customWidth="1" min="3" max="3" width="20.14"/>
-    <col customWidth="1" min="4" max="4" width="17.43"/>
-    <col customWidth="1" min="5" max="5" width="13.0"/>
-    <col customWidth="1" min="6" max="26" width="9.14"/>
+    <col min="1" max="2" width="6.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="26" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -828,7 +846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>-33.72</v>
       </c>
@@ -848,7 +866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>-34.36</v>
       </c>
@@ -868,9 +886,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>-34.41</v>
+        <v>-34.409999999999997</v>
       </c>
       <c r="B4" s="2">
         <v>-56.39</v>
@@ -888,7 +906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>-31.87</v>
       </c>
@@ -908,7 +926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>-32.4</v>
       </c>
@@ -928,9 +946,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>-33.8</v>
+        <v>-33.799999999999997</v>
       </c>
       <c r="B7" s="2">
         <v>-58.26</v>
@@ -948,9 +966,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>-34.2</v>
+        <v>-34.200000000000003</v>
       </c>
       <c r="B8" s="2">
         <v>-54.76</v>
@@ -968,9 +986,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>-33.16</v>
+        <v>-33.159999999999997</v>
       </c>
       <c r="B9" s="2">
         <v>-57.12</v>
@@ -988,7 +1006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>-32.61</v>
       </c>
@@ -1008,7 +1026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>-30.39</v>
       </c>
@@ -1028,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>-30.71</v>
       </c>
@@ -1048,7 +1066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>-33.96</v>
       </c>
@@ -1068,7 +1086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>-32.4</v>
       </c>
@@ -1088,7 +1106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>-30.78</v>
       </c>
@@ -1108,7 +1126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>-30.29</v>
       </c>
@@ -1128,9 +1146,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>-32.88</v>
+        <v>-32.880000000000003</v>
       </c>
       <c r="B17" s="2">
         <v>-55.62</v>
@@ -1148,7 +1166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>-33.46</v>
       </c>
@@ -1168,9 +1186,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>-33.87</v>
+        <v>-33.869999999999997</v>
       </c>
       <c r="B19" s="2">
         <v>-57.37</v>
@@ -1188,7 +1206,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>-34.83</v>
       </c>
@@ -1208,7 +1226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>-34.1</v>
       </c>
@@ -1228,7 +1246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>-30.88</v>
       </c>
@@ -1248,7 +1266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>-30.78</v>
       </c>
@@ -1268,7 +1286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>-32.51</v>
       </c>
@@ -1276,11 +1294,11 @@
         <v>-57.16</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E24" s="1" t="s">
         <v>8</v>
       </c>
@@ -1288,7 +1306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>-32.36</v>
       </c>
@@ -1296,7 +1314,7 @@
         <v>-53.88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>14</v>
@@ -1308,7 +1326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>-33.26</v>
       </c>
@@ -1316,7 +1334,7 @@
         <v>-53.79</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>7</v>
@@ -1328,15 +1346,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>-32.13</v>
+        <v>-32.130000000000003</v>
       </c>
       <c r="B27" s="2">
         <v>-53.75</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>14</v>
@@ -1348,7 +1366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>-30.62</v>
       </c>
@@ -1356,7 +1374,7 @@
         <v>-56.66</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>24</v>
@@ -1368,15 +1386,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>-33.09</v>
+        <v>-33.090000000000003</v>
       </c>
       <c r="B29" s="2">
         <v>-55.14</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>33</v>
@@ -1388,15 +1406,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>-33.88</v>
+        <v>-33.880000000000003</v>
       </c>
       <c r="B30" s="3">
         <v>-55.53</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>12</v>
@@ -1408,7 +1426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>-32.61</v>
       </c>
@@ -1416,7 +1434,7 @@
         <v>-54.59</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>14</v>
@@ -1428,7 +1446,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>-33.71</v>
       </c>
@@ -1436,7 +1454,7 @@
         <v>-56.67</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>22</v>
@@ -1448,7 +1466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>-34.24</v>
       </c>
@@ -1456,7 +1474,7 @@
         <v>-55.92</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>12</v>
@@ -1468,19 +1486,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <v>-34.13</v>
+        <v>-34.130000000000003</v>
       </c>
       <c r="B34" s="4">
         <v>-56.69</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
       </c>
@@ -1488,7 +1506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>-31.65</v>
       </c>
@@ -1496,11 +1514,11 @@
         <v>-57.89</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="E35" s="1" t="s">
         <v>8</v>
       </c>
@@ -1508,7 +1526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>-33.9</v>
       </c>
@@ -1516,11 +1534,11 @@
         <v>-58.1</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="E36" s="1" t="s">
         <v>8</v>
       </c>
@@ -1528,7 +1546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>-32.22</v>
       </c>
@@ -1536,7 +1554,7 @@
         <v>-55.72</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>16</v>
@@ -1548,18 +1566,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>-34.45</v>
+        <v>-34.450000000000003</v>
       </c>
       <c r="B38" s="4">
         <v>-57.76</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>8</v>
@@ -1568,7 +1586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>-31.34</v>
       </c>
@@ -1576,7 +1594,7 @@
         <v>-57.4</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>30</v>
@@ -1588,7 +1606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>-31.09</v>
       </c>
@@ -1596,7 +1614,7 @@
         <v>-57.02</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>30</v>
@@ -1608,18 +1626,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <v>-34.0</v>
+        <v>-34</v>
       </c>
       <c r="B41" s="4">
         <v>-57.64</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>8</v>
@@ -1628,7 +1646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>-30.58</v>
       </c>
@@ -1636,7 +1654,7 @@
         <v>-57.68</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>24</v>
@@ -1648,7 +1666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>-30.43</v>
       </c>
@@ -1656,7 +1674,7 @@
         <v>-56.54</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>24</v>
@@ -1668,7 +1686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>-34.33</v>
       </c>
@@ -1676,10 +1694,10 @@
         <v>-57.26</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
@@ -1688,18 +1706,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>-34.16</v>
+        <v>-34.159999999999997</v>
       </c>
       <c r="B45" s="4">
         <v>-58.03</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>8</v>
@@ -1708,7 +1726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>-34.06</v>
       </c>
@@ -1716,7 +1734,7 @@
         <v>-57.85</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>30</v>
@@ -1728,7 +1746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>-34.35</v>
       </c>
@@ -1736,7 +1754,7 @@
         <v>-54.79</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>20</v>
@@ -1748,7 +1766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>-30.61</v>
       </c>
@@ -1756,7 +1774,7 @@
         <v>-56.9</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>24</v>
@@ -1768,15 +1786,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>-32.13</v>
+        <v>-32.130000000000003</v>
       </c>
       <c r="B49" s="4">
         <v>-54.89</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>16</v>
@@ -1788,7 +1806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>-32.24</v>
       </c>
@@ -1796,7 +1814,7 @@
         <v>-54.99</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>16</v>
@@ -1808,18 +1826,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>-32.55</v>
+        <v>-32.549999999999997</v>
       </c>
       <c r="B51" s="4">
         <v>-56.82</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>8</v>
@@ -1828,7 +1846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>-31.77</v>
       </c>
@@ -1836,7 +1854,7 @@
         <v>-55.69</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>16</v>
@@ -1848,15 +1866,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>-32.73</v>
+        <v>-32.729999999999997</v>
       </c>
       <c r="B53" s="4">
         <v>-55.03</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>14</v>
@@ -1868,7 +1886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>-32.14</v>
       </c>
@@ -1876,7 +1894,7 @@
         <v>-56.11</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>16</v>
@@ -1888,7 +1906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>-30.75</v>
       </c>
@@ -1896,7 +1914,7 @@
         <v>-57.05</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>24</v>
@@ -1908,15 +1926,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>-33.52</v>
+        <v>-33.520000000000003</v>
       </c>
       <c r="B56" s="4">
         <v>-58.21</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>18</v>
@@ -1928,7 +1946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>-34.68</v>
       </c>
@@ -1936,7 +1954,7 @@
         <v>-55.7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>37</v>
@@ -1948,7 +1966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>-33.35</v>
       </c>
@@ -1968,7 +1986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>-34.35</v>
       </c>
@@ -1976,10 +1994,10 @@
         <v>-57.08</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>8</v>
@@ -1988,7 +2006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>-33.03</v>
       </c>
@@ -1996,10 +2014,10 @@
         <v>-57.27</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
@@ -2008,18 +2026,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>-33.98</v>
+        <v>-33.979999999999997</v>
       </c>
       <c r="B61" s="4">
         <v>-58.23</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>8</v>
@@ -2028,15 +2046,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>-31.71</v>
       </c>
       <c r="B62" s="4">
-        <v>-56.0</v>
+        <v>-56</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>16</v>
@@ -2048,7 +2066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>-33.06</v>
       </c>
@@ -2056,7 +2074,7 @@
         <v>-57.46</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>18</v>
@@ -2068,7 +2086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>-30.29</v>
       </c>
@@ -2076,7 +2094,7 @@
         <v>-56.82</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>24</v>
@@ -2088,18 +2106,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>-33.87</v>
+        <v>-33.869999999999997</v>
       </c>
       <c r="B65" s="4">
         <v>-57.37</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>8</v>
@@ -2108,7 +2126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>-34.08</v>
       </c>
@@ -2128,7 +2146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>-32.51</v>
       </c>
@@ -2136,7 +2154,7 @@
         <v>-54.53</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>14</v>
@@ -2148,18 +2166,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>-33.12</v>
+        <v>-33.119999999999997</v>
       </c>
       <c r="B68" s="4">
         <v>-58.26</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>8</v>
@@ -2168,15 +2186,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>-33.52</v>
+        <v>-33.520000000000003</v>
       </c>
       <c r="B69" s="4">
         <v>-56.41</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>12</v>
@@ -2188,18 +2206,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>-33.2</v>
+        <v>-33.200000000000003</v>
       </c>
       <c r="B70" s="4">
         <v>-53.8</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>8</v>
@@ -2208,7 +2226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>-32.35</v>
       </c>
@@ -2216,10 +2234,10 @@
         <v>-57.2</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>8</v>
@@ -2228,7 +2246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>-31.95</v>
       </c>
@@ -2236,7 +2254,7 @@
         <v>-54.12</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>14</v>
@@ -2248,7 +2266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>-32.99</v>
       </c>
@@ -2256,10 +2274,10 @@
         <v>-54.56</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>8</v>
@@ -2268,7 +2286,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>-30.43</v>
       </c>
@@ -2276,7 +2294,7 @@
         <v>-56.78</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>24</v>
@@ -2288,15 +2306,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>-33.45</v>
+        <v>-33.450000000000003</v>
       </c>
       <c r="B75" s="4">
         <v>-54.53</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>27</v>
@@ -2308,7 +2326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>-33.92</v>
       </c>
@@ -2316,7 +2334,7 @@
         <v>-56.23</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>12</v>
@@ -2328,7 +2346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>-32.72</v>
       </c>
@@ -2336,7 +2354,7 @@
         <v>-55.57</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>33</v>
@@ -2348,7 +2366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>-31.5</v>
       </c>
@@ -2356,7 +2374,7 @@
         <v>-57.52</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>30</v>
@@ -2368,7 +2386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>-34.14</v>
       </c>
@@ -2376,10 +2394,10 @@
         <v>-56.95</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>8</v>
@@ -2388,15 +2406,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>-33.38</v>
+        <v>-33.380000000000003</v>
       </c>
       <c r="B80" s="4">
         <v>-57.16</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>22</v>
@@ -2408,7 +2426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>-34.04</v>
       </c>
@@ -2416,7 +2434,7 @@
         <v>-54.78</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>27</v>
@@ -2428,7 +2446,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>-34.26</v>
       </c>
@@ -2436,7 +2454,7 @@
         <v>-54.95</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>27</v>
@@ -2448,15 +2466,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>-34.63</v>
+        <v>-34.630000000000003</v>
       </c>
       <c r="B83" s="4">
         <v>-55.04</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>20</v>
@@ -2468,7 +2486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>-34.78</v>
       </c>
@@ -2476,10 +2494,10 @@
         <v>-56.26</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>8</v>
@@ -2488,7 +2506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>-32.35</v>
       </c>
@@ -2496,7 +2514,7 @@
         <v>-54.19</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>14</v>
@@ -2508,7 +2526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>-34.28</v>
       </c>
@@ -2516,7 +2534,7 @@
         <v>-56.21</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>12</v>
@@ -2528,7 +2546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>-33.25</v>
       </c>
@@ -2536,7 +2554,7 @@
         <v>-58.06</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>18</v>
@@ -2548,15 +2566,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
-        <v>-34.37</v>
+        <v>-34.369999999999997</v>
       </c>
       <c r="B88" s="4">
         <v>-55.23</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>27</v>
@@ -2568,7 +2586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>-31.57</v>
       </c>
@@ -2576,10 +2594,10 @@
         <v>-55.47</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>8</v>
@@ -2588,7 +2606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>-31.6</v>
       </c>
@@ -2596,10 +2614,10 @@
         <v>-54.97</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>8</v>
@@ -2608,15 +2626,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
-        <v>-33.05</v>
+        <v>-33.049999999999997</v>
       </c>
       <c r="B91" s="4">
         <v>-56.49</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>33</v>
@@ -2628,7 +2646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>-34.28</v>
       </c>
@@ -2636,10 +2654,10 @@
         <v>-57.23</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>8</v>
@@ -2648,18 +2666,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
-        <v>-33.87</v>
+        <v>-33.869999999999997</v>
       </c>
       <c r="B93" s="4">
-        <v>58.4</v>
+        <v>-58.4</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>8</v>
@@ -2668,7 +2686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>-33.93</v>
       </c>
@@ -2676,10 +2694,10 @@
         <v>-57.81</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>8</v>
@@ -2688,7 +2706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>-33.5</v>
       </c>
@@ -2696,7 +2714,7 @@
         <v>-57.79</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>18</v>
@@ -2708,7 +2726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>-30.78</v>
       </c>
@@ -2716,7 +2734,7 @@
         <v>-56.78</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>24</v>
@@ -2728,18 +2746,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
-        <v>-32.55</v>
+        <v>-32.549999999999997</v>
       </c>
       <c r="B97" s="4">
         <v>-57.39</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>8</v>
@@ -2748,7 +2766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>-30.48</v>
       </c>
@@ -2756,7 +2774,7 @@
         <v>-57.13</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>24</v>
@@ -2768,18 +2786,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
-        <v>-32.34</v>
+        <v>-32.340000000000003</v>
       </c>
       <c r="B99" s="4">
         <v>-58.03</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>8</v>
@@ -2788,7 +2806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>-32.49</v>
       </c>
@@ -2796,7 +2814,7 @@
         <v>-56.35</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>16</v>
@@ -2808,18 +2826,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>-32.37</v>
+        <v>-32.369999999999997</v>
       </c>
       <c r="B101" s="4">
         <v>-57.61</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>8</v>
@@ -2828,7 +2846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>-30.46</v>
       </c>
@@ -2836,7 +2854,7 @@
         <v>-56.42</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>24</v>
@@ -2848,7 +2866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>-33.74</v>
       </c>
@@ -2856,7 +2874,7 @@
         <v>-54.75</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>27</v>
@@ -2868,7 +2886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>-33.89</v>
       </c>
@@ -2876,7 +2894,7 @@
         <v>-55.16</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>27</v>
@@ -2888,15 +2906,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4">
-        <v>-33.48</v>
+        <v>-33.479999999999997</v>
       </c>
       <c r="B105" s="4">
         <v>-56.15</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>12</v>
@@ -2908,7 +2926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4">
         <v>-34.86</v>
       </c>
@@ -2916,10 +2934,10 @@
         <v>-56.2</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>8</v>
@@ -2928,7 +2946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4">
         <v>-31.28</v>
       </c>
@@ -2936,7 +2954,7 @@
         <v>-57.13</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>30</v>
@@ -2948,7 +2966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4">
         <v>-32.82</v>
       </c>
@@ -2956,7 +2974,7 @@
         <v>-56.49</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>33</v>
@@ -2968,7 +2986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4">
         <v>-32.81</v>
       </c>
@@ -2976,10 +2994,10 @@
         <v>-57.04</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
@@ -2988,7 +3006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4">
         <v>-33.69</v>
       </c>
@@ -2996,7 +3014,7 @@
         <v>-57.53</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>18</v>
@@ -3008,7 +3026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4">
         <v>-32.39</v>
       </c>
@@ -3016,10 +3034,10 @@
         <v>-57.96</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>8</v>
@@ -3028,7 +3046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
         <v>-34.96</v>
       </c>
@@ -3036,7 +3054,7 @@
         <v>-54.95</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>20</v>
@@ -3048,7 +3066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4">
         <v>-33.82</v>
       </c>
@@ -3056,7 +3074,7 @@
         <v>-57.01</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>22</v>
@@ -3068,7 +3086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4">
         <v>-31.93</v>
       </c>
@@ -3076,10 +3094,10 @@
         <v>-57.89</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>8</v>
@@ -3088,7 +3106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4">
         <v>-31.35</v>
       </c>
@@ -3096,7 +3114,7 @@
         <v>-56.39</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>30</v>
@@ -3108,7 +3126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4">
         <v>-30.89</v>
       </c>
@@ -3116,10 +3134,10 @@
         <v>-55.54</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>8</v>
@@ -3128,7 +3146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4">
         <v>-34.49</v>
       </c>
@@ -3148,7 +3166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4">
         <v>-33.18</v>
       </c>
@@ -3156,7 +3174,7 @@
         <v>-55.69</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>33</v>
@@ -3168,7 +3186,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4">
         <v>-31.43</v>
       </c>
@@ -3188,15 +3206,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4">
-        <v>-34.45</v>
+        <v>-34.450000000000003</v>
       </c>
       <c r="B120" s="4">
         <v>-56.07</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>37</v>
@@ -3208,7 +3226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4">
         <v>-34.03</v>
       </c>
@@ -3216,7 +3234,7 @@
         <v>-55.88</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>12</v>
@@ -3228,15 +3246,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4">
-        <v>-33.87</v>
+        <v>-33.869999999999997</v>
       </c>
       <c r="B122" s="4">
         <v>-56.75</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>22</v>
@@ -3248,7 +3266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
         <v>-34.53</v>
       </c>
@@ -3256,7 +3274,7 @@
         <v>-55.87</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>37</v>
@@ -3268,18 +3286,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4">
-        <v>-32.66</v>
+        <v>-32.659999999999997</v>
       </c>
       <c r="B124" s="4">
         <v>-58.13</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>8</v>
@@ -3288,7 +3306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4">
         <v>-32.83</v>
       </c>
@@ -3296,10 +3314,10 @@
         <v>-57.73</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>8</v>
@@ -3308,7 +3326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4">
         <v>-33.79</v>
       </c>
@@ -3316,7 +3334,7 @@
         <v>-57.49</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>18</v>
@@ -3328,7 +3346,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4">
         <v>-30.99</v>
       </c>
@@ -3336,7 +3354,7 @@
         <v>-56.22</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>30</v>
@@ -3348,235 +3366,235 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4">
-        <v>-33.33</v>
+        <v>-31</v>
       </c>
       <c r="B128" s="4">
-        <v>-55.62</v>
+        <v>-56.87</v>
       </c>
       <c r="C128" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="4">
+        <v>-33.35</v>
+      </c>
+      <c r="B129" s="4">
+        <v>-56.51</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="4">
+        <v>-34.340000000000003</v>
+      </c>
+      <c r="B130" s="4">
+        <v>-55.76</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A131" s="4">
+        <v>-31.87</v>
+      </c>
+      <c r="B131" s="4">
+        <v>-56.24</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="4">
+        <v>-34.26</v>
+      </c>
+      <c r="B132" s="4">
+        <v>-57.61</v>
+      </c>
+      <c r="C132" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="4">
-        <v>-33.72</v>
-      </c>
-      <c r="B129" s="4">
-        <v>-56.32</v>
-      </c>
-      <c r="C129" s="1" t="s">
+      <c r="D132" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="4">
+        <v>-30.94</v>
+      </c>
+      <c r="B133" s="4">
+        <v>-57.52</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="4">
-        <v>-31.0</v>
-      </c>
-      <c r="B130" s="4">
-        <v>-56.87</v>
-      </c>
-      <c r="C130" s="1" t="s">
+      <c r="D133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="4">
+        <v>-30.43</v>
+      </c>
+      <c r="B134" s="4">
+        <v>-57.44</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D134" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E130" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="4">
-        <v>-33.35</v>
-      </c>
-      <c r="B131" s="4">
-        <v>-56.51</v>
-      </c>
-      <c r="C131" s="1" t="s">
+      <c r="E134" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="4">
+        <v>-31.19</v>
+      </c>
+      <c r="B135" s="4">
+        <v>-55.77</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="4">
-        <v>-34.34</v>
-      </c>
-      <c r="B132" s="4">
-        <v>-55.76</v>
-      </c>
-      <c r="C132" s="1" t="s">
+      <c r="D135" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="4">
+        <v>-33.22</v>
+      </c>
+      <c r="B136" s="4">
+        <v>-54.38</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="4">
+        <v>-32.270000000000003</v>
+      </c>
+      <c r="B137" s="4">
+        <v>-54.18</v>
+      </c>
+      <c r="C137" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="4">
-        <v>-31.87</v>
-      </c>
-      <c r="B133" s="4">
-        <v>-56.24</v>
-      </c>
-      <c r="C133" s="1" t="s">
+      <c r="D137" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A138" s="4">
+        <v>-33.53</v>
+      </c>
+      <c r="B138" s="4">
+        <v>-56.91</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D133" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="4">
-        <v>-34.26</v>
-      </c>
-      <c r="B134" s="4">
-        <v>-57.61</v>
-      </c>
-      <c r="C134" s="1" t="s">
+      <c r="D138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A139" s="4">
+        <v>-32.83</v>
+      </c>
+      <c r="B139" s="4">
+        <v>-54.76</v>
+      </c>
+      <c r="C139" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="4">
-        <v>-30.94</v>
-      </c>
-      <c r="B135" s="4">
-        <v>-57.52</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="4">
-        <v>-30.43</v>
-      </c>
-      <c r="B136" s="4">
-        <v>-57.44</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="4">
-        <v>-31.19</v>
-      </c>
-      <c r="B137" s="4">
-        <v>-55.77</v>
-      </c>
-      <c r="C137" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="4">
-        <v>-33.22</v>
-      </c>
-      <c r="B138" s="4">
-        <v>-54.38</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="4">
-        <v>-32.27</v>
-      </c>
-      <c r="B139" s="4">
-        <v>-54.18</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>14</v>
@@ -3588,155 +3606,155 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4">
-        <v>-33.53</v>
+        <v>-31.82</v>
       </c>
       <c r="B140" s="4">
-        <v>-56.91</v>
+        <v>-56.17</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="4">
+        <v>-34.03</v>
+      </c>
+      <c r="B141" s="4">
+        <v>-54.28</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A142" s="4">
+        <v>-31.77</v>
+      </c>
+      <c r="B142" s="4">
+        <v>-54.69</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" s="4">
+        <v>-34.19</v>
+      </c>
+      <c r="B143" s="4">
+        <v>-56.34</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A144" s="4">
+        <v>-34.29</v>
+      </c>
+      <c r="B144" s="4">
+        <v>-56.39</v>
+      </c>
+      <c r="C144" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="4">
-        <v>-32.83</v>
-      </c>
-      <c r="B141" s="4">
-        <v>-54.76</v>
-      </c>
-      <c r="C141" s="1" t="s">
+      <c r="D144" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="4">
+        <v>-33.119999999999997</v>
+      </c>
+      <c r="B145" s="4">
+        <v>-57.64</v>
+      </c>
+      <c r="C145" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D141" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="4">
-        <v>-31.82</v>
-      </c>
-      <c r="B142" s="4">
-        <v>-56.17</v>
-      </c>
-      <c r="C142" s="1" t="s">
+      <c r="D145" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="4">
+        <v>-34.590000000000003</v>
+      </c>
+      <c r="B146" s="4">
+        <v>-55.46</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="4">
-        <v>-34.03</v>
-      </c>
-      <c r="B143" s="4">
-        <v>-54.28</v>
-      </c>
-      <c r="C143" s="1" t="s">
+      <c r="D146" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="4">
+        <v>-33.39</v>
+      </c>
+      <c r="B147" s="4">
+        <v>-58.32</v>
+      </c>
+      <c r="C147" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="4">
-        <v>-31.77</v>
-      </c>
-      <c r="B144" s="4">
-        <v>-54.69</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="4">
-        <v>-34.19</v>
-      </c>
-      <c r="B145" s="4">
-        <v>-56.34</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="4">
-        <v>-34.29</v>
-      </c>
-      <c r="B146" s="4">
-        <v>-56.39</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="4">
-        <v>-33.12</v>
-      </c>
-      <c r="B147" s="4">
-        <v>-57.64</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>18</v>
@@ -3748,39 +3766,39 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4">
-        <v>-34.59</v>
+        <v>-32.68</v>
       </c>
       <c r="B148" s="4">
-        <v>-55.46</v>
+        <v>-57.64</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D148" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="4">
+        <v>-33.520000000000003</v>
+      </c>
+      <c r="B149" s="4">
+        <v>-54.94</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="4">
-        <v>-33.39</v>
-      </c>
-      <c r="B149" s="4">
-        <v>-58.32</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E149" s="1" t="s">
         <v>8</v>
       </c>
@@ -3788,903 +3806,861 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="4">
-        <v>-32.68</v>
-      </c>
-      <c r="B150" s="4">
-        <v>-57.64</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="4">
-        <v>-33.52</v>
-      </c>
-      <c r="B151" s="4">
-        <v>-54.94</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="5"/>
-      <c r="B152" s="5"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
+    </row>
+    <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <autoFilter ref="$A$1:$F$151"/>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="A1:F149" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>